--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422981.8235728967</v>
+        <v>422982</v>
       </c>
       <c r="R2" t="n">
-        <v>6387823.769728828</v>
+        <v>6387824</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107331</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107338</v>
+        <v>107342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107366</v>
+        <v>107376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38072-2021 artfynd.xlsx
+++ b/artfynd/A 38072-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>73982578</v>
       </c>
       <c r="B2" t="n">
-        <v>107376</v>
+        <v>107907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,6 +774,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74783248</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L9 Fållegärde 1350 m ONO, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>422982</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6387824</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norra Unnaryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D8e 0948. SOM: Polygala vulgaris. LEG: Lennart Stenberg, Lennart Ståhl</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
